--- a/data/trans_dic/IP25A_R_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP25A_R_2023-Edad-trans_dic.xlsx
@@ -490,18 +490,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 98,91%)</t>
+          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,02; 15,85</t>
+          <t>2,94; 12,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 16,27</t>
+          <t>4,49; 15,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,13; 13,17</t>
+          <t>4,77; 12,51</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,51; 17,11</t>
+          <t>9,62; 18,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,99; 19,45</t>
+          <t>8,88; 17,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,39; 16,91</t>
+          <t>10,29; 16,5</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,76; 25,95</t>
+          <t>10,9; 20,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,95; 20,16</t>
+          <t>11,99; 21,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,11; 21,17</t>
+          <t>12,34; 19,32</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,49; 16,57</t>
+          <t>10,63; 18,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,12; 18,19</t>
+          <t>9,44; 16,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,16; 15,86</t>
+          <t>11,0; 16,26</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,06; 16,42</t>
+          <t>11,64; 16,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,52; 16,22</t>
+          <t>11,52; 16,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,14; 15,79</t>
+          <t>12,11; 15,52</t>
         </is>
       </c>
     </row>
@@ -825,18 +825,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 98,91%)</t>
+          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5076</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9787</t>
+          <t>7870</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2252; 8886</t>
+          <t>1443; 6272</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2294; 9716</t>
+          <t>2283; 7898</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5938; 15253</t>
+          <t>4769; 12509</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>19166</t>
+          <t>21683</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>25950</t>
+          <t>18330</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45116</t>
+          <t>40013</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13227; 26584</t>
+          <t>15155; 29763</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18245; 35508</t>
+          <t>12599; 25463</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35120; 57144</t>
+          <t>30820; 49419</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32905</t>
+          <t>30301</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31773</t>
+          <t>28649</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64677</t>
+          <t>58949</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23706; 44718</t>
+          <t>21819; 40681</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23262; 42829</t>
+          <t>20837; 37944</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50454; 81459</t>
+          <t>46166; 72258</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>48</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>32947</t>
+          <t>40494</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>41526</t>
+          <t>32620</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>74474</t>
+          <t>73114</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22971; 44815</t>
+          <t>30951; 54101</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30765; 55299</t>
+          <t>23737; 41799</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>58341; 91115</t>
+          <t>59678; 88212</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>125</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>89730</t>
+          <t>96010</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>104325</t>
+          <t>83936</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>194055</t>
+          <t>179946</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>72364; 107420</t>
+          <t>81248; 112983</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>87401; 123075</t>
+          <t>71183; 99093</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>171524; 223073</t>
+          <t>159367; 204211</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP25A_R_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP25A_R_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 98,91%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>7,19%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8,53%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7,87%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2,94; 12,77</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4,49; 15,53</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4,77; 12,51</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>13,77%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>12,92%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>13,36%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>9,62; 18,89</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8,88; 17,94</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10,29; 16,5</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>15,14%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>16,48%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>15,76%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>10,9; 20,33</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>11,99; 21,83</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>12,34; 19,32</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>13,91%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13,48%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>10,63; 18,58</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>9,44; 16,62</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11,0; 16,26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>13,76%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>13,58%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>13,67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>11,64; 16,19</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>11,52; 16,03</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12,11; 15,52</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.07191799148348639</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.08530220253468335</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.07872634720529439</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4338</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7870</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.02938057695244956</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.04490389070755643</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.04770739063073494</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1443; 6272</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2283; 7898</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4769; 12509</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.1277002107610699</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.1553201262631946</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.1251343713713589</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.1376503867447399</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1291548072257865</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1336239010476858</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>21683</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>18330</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>40013</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.09620562709257917</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.08877769968189266</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.102925230077758</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>15155; 29763</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>12599; 25463</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>30820; 49419</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.1889470851554319</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.1794134906053853</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.1650355354690223</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.1514078069532142</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1647915334653081</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1576294838353266</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>30301</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>28649</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>58949</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.1090255451601756</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.119858802532034</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.1234465647896683</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>21819; 40681</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>20837; 37944</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>46166; 72258</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.2032759141234995</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.218260611957198</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.1932163729089725</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1390879225013928</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1297293178829364</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1347509310002679</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>40494</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>32620</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>73114</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.1063102779542192</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.094399943927906</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.1099875883366333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>30951; 54101</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>23737; 41799</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>59678; 88212</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.1858250359191464</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.1662327957679334</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.1625764257541588</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.1375691519454732</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.1358044245993105</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.136740316576032</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>96010</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>83936</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>179946</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.1164182585190881</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.1151703064047047</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.1211023747830282</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>81248; 112983</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>71183; 99093</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>159367; 204211</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.1618900306941603</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.1603264590042789</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.1551790388306557</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 98,91%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>3532</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>4338</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>7870</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1443</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>2283</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>4769</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>6272</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>7898</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>12509</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>21683</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>18330</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>40013</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>15155</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>12599</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>30820</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>29763</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>25463</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>49419</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>30301</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>28649</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>58949</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>21819</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>20837</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>46166</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>40681</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>37944</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>72258</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>40494</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>32620</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>73114</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>30951</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>23737</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>59678</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>54101</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>41799</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>88212</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>125</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>96010</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>83936</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>179946</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>81248</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>71183</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>159367</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>112983</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>99093</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>204211</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>